--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/11_Anotacijos_logai/11_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/11_Anotacijos_logai/11_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\11_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC7A920-79F2-429C-95E0-059F8AAB4BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D131E33B-96F8-40D0-8D74-C7A7CB5E19EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,6 +180,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -347,16 +348,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -720,7 +721,8 @@
       <c r="D2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="4" t="b">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3"/>
@@ -754,7 +756,7 @@
       <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="b">
+      <c r="F3" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -788,7 +790,7 @@
       <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="4" t="b">
+      <c r="F4" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -820,7 +822,7 @@
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="b">
+      <c r="F5" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
@@ -854,7 +856,7 @@
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4" t="b">
+      <c r="F6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3"/>
@@ -886,7 +888,7 @@
       <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="4" t="b">
+      <c r="F7" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3"/>
@@ -918,7 +920,7 @@
       <c r="D8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4" t="b">
+      <c r="F8" s="4" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="4"/>
@@ -949,7 +951,7 @@
       <c r="D9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="4" t="b">
+      <c r="F9" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3"/>
@@ -968,7 +970,7 @@
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="4" t="b">
+      <c r="F10" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="15" t="s">
@@ -989,7 +991,7 @@
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="4" t="b">
+      <c r="F11" s="4" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="7"/>

--- a/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/11_Anotacijos_logai/11_Anotavimo_logas.xlsx
+++ b/0_SELECT_ZIVE_DATA_2023/AnotacijosLogai/11_Anotacijos_logai/11_Anotavimo_logas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\kesju\DI\2025_ZIVEO\PROJECT_TRAIN_UNET\0_SELECT_ZIVE_DATA_2023\AnotacijosLogai\11_Anotacijos_logai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D131E33B-96F8-40D0-8D74-C7A7CB5E19EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC295384-164D-424C-901F-28AD3023343B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -762,7 +762,9 @@
       <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="11" t="s">
@@ -796,7 +798,9 @@
       <c r="G4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="11"/>
@@ -828,7 +832,9 @@
       <c r="G5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="11" t="s">
@@ -976,7 +982,9 @@
       <c r="G10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="4" t="b">
+        <v>1</v>
+      </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
